--- a/test_data/test_workshops_1.xlsx
+++ b/test_data/test_workshops_1.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,100 +438,5160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F2 L2</t>
+          <t>Felix Meyer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F1 L1</t>
+          <t>Olivia Klein</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F2 L2</t>
+          <t>Paul Neumann</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F1 L1</t>
+          <t>Jonas Klein</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F1 L1</t>
+          <t>Felix Neumann</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lena Weber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Clara Lange</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clara Koch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sara Schmidt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mia Hartmann</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tim Wolf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paul Müller</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Laura Müller</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Felix Hoffmann</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Paul Krüger</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tim Lange</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Clara Weber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sara Klein</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hannah Schneider</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Max Lange</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ben Schulz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ben Schmidt</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Emma Lange</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Anna Schneider</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Noah Koch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lena Fischer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hannah Fischer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tim Meyer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mia Klein</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Greta Müller</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Greta Hartmann</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ben Hartmann</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mia Schneider</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Felix Hartmann</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hannah Schulz</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tim Krüger</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jonas Schulz</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Max Müller</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Workshop6</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Olivia Wolf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Noah Krüger</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Max Schulz</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mia Schulz</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lena Hartmann</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Felix Wagner</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Greta Schneider</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Paul Hartmann</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nina Neumann</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Anna Lange</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Emma Schmidt</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Jonas Fischer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hannah Neumann</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Max Schwarz</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hannah Wagner</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>David Becker</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sara Neumann</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Nina Wolf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Laura Krüger</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lena Schmidt</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Paul Weber</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Laura Weber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hannah Wolf</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Olivia Müller</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ben Schwarz</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Leon Hartmann</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Max Weber</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jonas Wagner</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nina Fischer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nina Becker</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Olivia Zimmermann</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tim Schwarz</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Laura Hoffmann</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mia Weber</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Noah Müller</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Anna Becker</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Felix Koch</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jonas Schneider</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Greta Wagner</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Leon Hartmann</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tim Müller</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sara Wolf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Emma Klein</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tim Weber</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Emma Schmidt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Noah Krüger</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Greta Wagner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Olivia Müller</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F2 L2</t>
+          <t>Leon Hartmann</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sara Klein</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Felix Wagner</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tim Krüger</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nina Neumann</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nina Becker</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Laura Weber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Felix Hoffmann</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hannah Wagner</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Max Schulz</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nina Wolf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Noah Müller</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Felix Hartmann</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hannah Fischer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tim Meyer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Greta Hartmann</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Felix Meyer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Leon Hartmann</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Felix Neumann</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lena Fischer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mia Klein</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Paul Krüger</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Olivia Klein</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sara Neumann</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mia Schulz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Max Weber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jonas Wagner</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tim Weber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Anna Schneider</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Clara Lange</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>David Becker</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mia Weber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hannah Schneider</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Paul Müller</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hannah Wolf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tim Lange</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jonas Schneider</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Clara Weber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Noah Koch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tim Müller</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mia Schneider</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Lena Schmidt</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Max Müller</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Greta Müller</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Paul Weber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ben Schmidt</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Olivia Zimmermann</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Laura Hoffmann</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Emma Lange</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Max Lange</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Jonas Fischer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Jonas Klein</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Greta Schneider</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Anna Becker</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sara Wolf</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sara Schmidt</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Emma Klein</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Jonas Schulz</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Anna Lange</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Felix Koch</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Olivia Wolf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Laura Müller</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nina Fischer</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tim Wolf</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ben Hartmann</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tim Schwarz</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Hannah Neumann</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Max Schwarz</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Paul Neumann</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Clara Koch</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ben Schwarz</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Lena Hartmann</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Laura Krüger</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Paul Hartmann</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lena Weber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hannah Schulz</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ben Schulz</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mia Hartmann</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ben Hartmann</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hannah Neumann</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Laura Müller</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Max Schwarz</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lena Fischer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paul Hartmann</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hannah Schulz</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Emma Klein</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Workshop1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ben Schulz</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Emma Schmidt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anna Schneider</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>David Becker</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Leon Hartmann</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mia Schulz</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Laura Krüger</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Workshop2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Greta Müller</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Felix Koch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tim Schwarz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Paul Neumann</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jonas Schneider</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Olivia Müller</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mia Weber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Noah Koch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hannah Fischer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tim Krüger</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tim Meyer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Workshop3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tim Weber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Felix Hoffmann</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Clara Koch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Greta Wagner</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mia Schneider</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lena Weber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Paul Weber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Anna Lange</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Workshop4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tim Wolf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Paul Müller</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Olivia Klein</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sara Neumann</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lena Hartmann</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Leon Hartmann</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Workshop5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Laura Weber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Laura Hoffmann</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Noah Müller</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Jonas Wagner</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Felix Hartmann</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nina Fischer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sara Schmidt</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Jonas Schulz</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Emma Zimmermann</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Olivia Wolf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hannah Wolf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sara Klein</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hannah Schneider</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Max Weber</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Anna Becker</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sara Wolf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Leon Lange</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nina Becker</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Noah Krüger</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Nina Krüger</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Emma Lange</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Clara Lange</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Clara Weber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Emma Hartmann</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tim Müller</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lena Schmidt</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tim Hartmann</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Max Müller</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Laura Zimmermann</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mia Hartmann</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Felix Meyer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Paul Krüger</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hannah Wagner</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Jonas Klein</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ben Schwarz</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Greta Schneider</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Max Lange</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mia Klein</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nina Neumann</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mia Hoffmann</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nina Zimmermann</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ben Schmidt</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Olivia Zimmermann</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jonas Fischer</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tim Lange</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Max Schulz</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Felix Neumann</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nina Wolf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Felix Wagner</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mia Schwarz</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Greta Hartmann</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>7</t>
         </is>

--- a/test_data/test_workshops_1.xlsx
+++ b/test_data/test_workshops_1.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Felix Meyer</t>
+          <t>Max Wolf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Olivia Klein</t>
+          <t>Ben Wagner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paul Neumann</t>
+          <t>Hannah Graf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jonas Klein</t>
+          <t>Mia Müller</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Felix Neumann</t>
+          <t>Tim Fischer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lena Weber</t>
+          <t>Felix Meyer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Simon Hofer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -562,24 +562,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>Emma Gruber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Max Wagner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -591,12 +591,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Laura Gruber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Laura Koch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -625,12 +625,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clara Lange</t>
+          <t>Fabian Berger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -642,29 +642,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clara Koch</t>
+          <t>Lisa Richter</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Matteo Weber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Fabian Graf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -693,12 +693,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara Schmidt</t>
+          <t>Sarah Hofer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -710,12 +710,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mia Hartmann</t>
+          <t>Jonas Bauer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tim Wolf</t>
+          <t>Clara Koch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -744,29 +744,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paul Müller</t>
+          <t>Simon Berger</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Laura Müller</t>
+          <t>Felix Gruber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Felix Hoffmann</t>
+          <t>Moritz Leitner</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Paul Krüger</t>
+          <t>Amelie Koch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -812,12 +812,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tim Lange</t>
+          <t>Emma Meyer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clara Weber</t>
+          <t>Anna Meyer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -846,46 +846,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sara Klein</t>
+          <t>Mia Wolf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hannah Schneider</t>
+          <t>Paul Kraus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Max Lange</t>
+          <t>Hannah Weber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -897,12 +897,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Simon Auer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -914,12 +914,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Moritz Wagner</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ben Schulz</t>
+          <t>Laura Schmidt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -948,12 +948,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -965,63 +965,63 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ben Schmidt</t>
+          <t>Clara Gruber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Emma Lange</t>
+          <t>Amelie Gruber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anna Schneider</t>
+          <t>Nina Schmidt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Noah Koch</t>
+          <t>Mia Bauer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1033,12 +1033,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Marie Weber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1050,131 +1050,131 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lena Fischer</t>
+          <t>Lena Kraus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hannah Fischer</t>
+          <t>Jakob Berger</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tim Meyer</t>
+          <t>David Schmidt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mia Klein</t>
+          <t>Tim Huber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Greta Müller</t>
+          <t>Mia Wagner</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Greta Hartmann</t>
+          <t>Leon Berger</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>David Maier</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ben Hartmann</t>
+          <t>Felix Huber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1186,63 +1186,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mia Schneider</t>
+          <t>Laura Wagner</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Felix Hartmann</t>
+          <t>Moritz Gruber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hannah Schulz</t>
+          <t>Emma Steiner</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tim Krüger</t>
+          <t>Felix Fischer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1254,12 +1254,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jonas Schulz</t>
+          <t>Hannah Maier</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Marie Wolf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1288,114 +1288,114 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Olivia Wolf</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Noah Krüger</t>
+          <t>Julia Richter</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Emma Müller</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>Ben Schmidt</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Max Schulz</t>
+          <t>Tim Wolf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mia Schulz</t>
+          <t>Anna Leitner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lena Hartmann</t>
+          <t>Sophie Fischer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1407,97 +1407,97 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Felix Wagner</t>
+          <t>Simon Weber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Greta Schneider</t>
+          <t>Amelie Gruber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Lisa Schmidt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Paul Hartmann</t>
+          <t>Lea Leitner</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nina Neumann</t>
+          <t>David Graf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anna Lange</t>
+          <t>Laura Richter</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1509,12 +1509,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Paul Meyer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1526,97 +1526,97 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Emma Schmidt</t>
+          <t>Elias Berger</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jonas Fischer</t>
+          <t>Max Huber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hannah Neumann</t>
+          <t>Marie Friedl</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Max Schwarz</t>
+          <t>Elias Graf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hannah Wagner</t>
+          <t>Clara Friedl</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David Becker</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1628,12 +1628,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sara Neumann</t>
+          <t>Mia Schmidt</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nina Wolf</t>
+          <t>Felix Weber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1662,63 +1662,63 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Laura Krüger</t>
+          <t>Nina Graf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lena Schmidt</t>
+          <t>Leon Graf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Paul Weber</t>
+          <t>Jonas Wagner</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Laura Weber</t>
+          <t>Marie Lang</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1730,12 +1730,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hannah Wolf</t>
+          <t>Anna Bauer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1747,12 +1747,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Olivia Müller</t>
+          <t>Ben Wagner</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1764,12 +1764,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ben Schwarz</t>
+          <t>Matteo Schmidt</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Moritz Fischer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Mia Steiner</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1815,12 +1815,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jonas Wagner</t>
+          <t>Julia Pichler</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nina Fischer</t>
+          <t>Clara Berger</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1849,63 +1849,63 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nina Becker</t>
+          <t>Moritz Hofer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Olivia Zimmermann</t>
+          <t>Felix Meyer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tim Schwarz</t>
+          <t>Nina Maier</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Laura Hoffmann</t>
+          <t>Fabian Wolf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1917,12 +1917,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mia Weber</t>
+          <t>Sarah Wolf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Noah Müller</t>
+          <t>Jonas Huber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1951,29 +1951,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Anna Becker</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Sophie Richter</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1985,80 +1985,80 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Felix Koch</t>
+          <t>Leon Auer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jonas Schneider</t>
+          <t>Simon Richter</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Greta Wagner</t>
+          <t>David Weber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Elias Graf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tim Müller</t>
+          <t>Lukas Wagner</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sara Wolf</t>
+          <t>Noah Fischer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Emma Klein</t>
+          <t>Lena Kraus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2121,15 +2121,1035 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Nina Wagner</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sarah Schmidt</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Mia Friedl</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Laura Berger</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Max Graf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sophie Wagner</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hannah Wolf</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lisa Berger</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nina Leitner</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Amelie Fischer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Max Koch</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Lisa Koch</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Elias Friedl</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Leon Maier</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Elias Hofer</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tim Leitner</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Katharina Hofer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Lisa Meyer</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Elias Lang</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Amelie Müller</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Lisa Pichler</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>David Kraus</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Jonas Hofer</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Lisa Schmidt</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Lisa Huber</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Mia Gruber</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Anna Kraus</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mia Fischer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sophie Bauer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Lukas Hofer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tim Kraus</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sarah Friedl</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Hannah Graf</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Katharina Müller</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Lisa Maier</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Lukas Maier</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Hannah Weber</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Emma Bauer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Lukas Bauer</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Lena Maier</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fabian Bauer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Paul Müller</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Elias Lang</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Clara Wolf</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Fabian Graf</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Felix Weber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Tim Leitner</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Anna Steiner</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Emma Gruber</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lisa Müller</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Fabian Weber</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>Workshop10</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Tim Weber</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Leon Hofer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Marie Lang</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>David Schmidt</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Jonas Auer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Tim Schwarz</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Marie Schwarz</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Emma Koch</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sarah Bauer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Nina Friedl</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Lukas Kraus</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2146,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2174,7 +3194,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Emma Schmidt</t>
+          <t>Sophie Wagner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2191,7 +3211,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Noah Krüger</t>
+          <t>Moritz Leitner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2208,7 +3228,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Emma Koch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2225,12 +3245,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Greta Wagner</t>
+          <t>Lisa Huber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2242,12 +3262,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Olivia Müller</t>
+          <t>Elias Berger</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2259,12 +3279,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Anna Kraus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2276,7 +3296,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sara Klein</t>
+          <t>Felix Fischer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2293,7 +3313,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Felix Wagner</t>
+          <t>Hannah Maier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2310,7 +3330,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tim Krüger</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2327,7 +3347,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nina Neumann</t>
+          <t>Ben Schmidt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2339,131 +3359,131 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nina Becker</t>
+          <t>Marie Friedl</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Laura Weber</t>
+          <t>Anna Leitner</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Felix Hoffmann</t>
+          <t>Sophie Bauer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hannah Wagner</t>
+          <t>Moritz Hofer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Max Schulz</t>
+          <t>Lisa Müller</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nina Wolf</t>
+          <t>Felix Meyer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Noah Müller</t>
+          <t>Lukas Hofer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Felix Hartmann</t>
+          <t>Nina Maier</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2480,12 +3500,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hannah Fischer</t>
+          <t>Ben Wagner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2497,12 +3517,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tim Meyer</t>
+          <t>Hannah Graf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2514,12 +3534,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Greta Hartmann</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2531,24 +3551,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Jonas Hofer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Felix Meyer</t>
+          <t>Tim Huber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2560,12 +3580,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Nina Graf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2577,12 +3597,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Mia Wagner</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2594,12 +3614,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Max Wagner</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2611,12 +3631,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Felix Neumann</t>
+          <t>David Maier</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2628,148 +3648,148 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lena Fischer</t>
+          <t>Felix Huber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Laura Wagner</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mia Klein</t>
+          <t>Lisa Koch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>Laura Koch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paul Krüger</t>
+          <t>Leon Maier</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Olivia Klein</t>
+          <t>Sarah Hofer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sara Neumann</t>
+          <t>David Weber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mia Schulz</t>
+          <t>Clara Berger</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Lukas Wagner</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2781,12 +3801,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jonas Wagner</t>
+          <t>Lisa Meyer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2798,12 +3818,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tim Weber</t>
+          <t>Nina Wagner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2815,12 +3835,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Anna Schneider</t>
+          <t>Felix Gruber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2832,12 +3852,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clara Lange</t>
+          <t>Max Wolf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2849,12 +3869,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>David Becker</t>
+          <t>Lisa Pichler</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2866,12 +3886,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mia Weber</t>
+          <t>Hannah Graf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2883,63 +3903,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hannah Schneider</t>
+          <t>Mia Schmidt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Felix Meyer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Emma Gruber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paul Müller</t>
+          <t>Lukas Maier</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2951,12 +3971,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hannah Wolf</t>
+          <t>Emma Meyer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2968,12 +3988,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tim Lange</t>
+          <t>Amelie Gruber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2985,12 +4005,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jonas Schneider</t>
+          <t>Emma Bauer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3002,12 +4022,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clara Weber</t>
+          <t>Marie Lang</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3019,63 +4039,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Lukas Bauer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Noah Koch</t>
+          <t>David Graf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tim Müller</t>
+          <t>Matteo Schmidt</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Sarah Bauer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3087,12 +4107,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mia Schneider</t>
+          <t>Mia Gruber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3104,12 +4124,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lena Schmidt</t>
+          <t>Nina Friedl</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3121,12 +4141,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Simon Auer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3138,12 +4158,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Greta Müller</t>
+          <t>Mia Friedl</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3155,29 +4175,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Paul Weber</t>
+          <t>Mia Müller</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ben Schmidt</t>
+          <t>Lena Kraus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3189,12 +4209,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Olivia Zimmermann</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3206,12 +4226,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Laura Hoffmann</t>
+          <t>Leon Graf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3223,12 +4243,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Emma Lange</t>
+          <t>Jonas Auer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3240,46 +4260,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Max Lange</t>
+          <t>Amelie Fischer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>Marie Schwarz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jonas Fischer</t>
+          <t>Max Koch</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3291,12 +4311,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jonas Klein</t>
+          <t>Fabian Bauer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3308,29 +4328,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Greta Schneider</t>
+          <t>Fabian Berger</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anna Becker</t>
+          <t>Paul Müller</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3342,12 +4362,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sara Wolf</t>
+          <t>Felix Weber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3359,12 +4379,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sara Schmidt</t>
+          <t>Julia Pichler</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3376,12 +4396,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Emma Klein</t>
+          <t>Emma Gruber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3393,12 +4413,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jonas Schulz</t>
+          <t>Laura Berger</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3410,29 +4430,29 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Anna Lange</t>
+          <t>David Kraus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Felix Koch</t>
+          <t>Marie Lang</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3444,12 +4464,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Olivia Wolf</t>
+          <t>Tim Fischer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3461,12 +4481,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Laura Müller</t>
+          <t>Hannah Weber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3478,12 +4498,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3495,12 +4515,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nina Fischer</t>
+          <t>Moritz Wagner</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3512,12 +4532,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Tim Leitner</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3529,12 +4549,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Marie Wolf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3546,12 +4566,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tim Wolf</t>
+          <t>Max Graf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3563,24 +4583,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ben Hartmann</t>
+          <t>Marie Weber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3597,12 +4617,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hannah Neumann</t>
+          <t>Simon Hofer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3614,12 +4634,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Max Schwarz</t>
+          <t>Lisa Maier</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3631,12 +4651,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Paul Neumann</t>
+          <t>Simon Weber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3648,12 +4668,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>David Schmidt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3665,12 +4685,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Clara Koch</t>
+          <t>Amelie Koch</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3682,12 +4702,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ben Schwarz</t>
+          <t>Jonas Wagner</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3699,12 +4719,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lena Hartmann</t>
+          <t>David Schmidt</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3716,80 +4736,80 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Mia Wolf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Laura Krüger</t>
+          <t>Lea Leitner</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Paul Hartmann</t>
+          <t>Laura Gruber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lena Weber</t>
+          <t>Moritz Fischer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hannah Schulz</t>
+          <t>Lisa Richter</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3801,12 +4821,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ben Schulz</t>
+          <t>Matteo Weber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3818,12 +4838,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>Anna Steiner</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3835,12 +4855,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3852,15 +4872,1035 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mia Fischer</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tim Wolf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Amelie Gruber</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Nina Schmidt</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Elias Graf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sarah Friedl</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Felix Weber</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lisa Schmidt</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Paul Kraus</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Moritz Gruber</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hannah Weber</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fabian Graf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Fabian Graf</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Jonas Bauer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Emma Müller</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Noah Fischer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hannah Wolf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Clara Friedl</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Katharina Müller</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Jakob Berger</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Lisa Berger</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fabian Wolf</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sarah Wolf</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nina Leitner</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Leon Berger</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Anna Bauer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ben Wagner</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Paul Meyer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sophie Richter</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Leon Auer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Laura Schmidt</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lukas Kraus</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Clara Koch</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tim Leitner</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Amelie Müller</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Fabian Weber</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Leon Hofer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Lisa Schmidt</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Jonas Huber</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Elias Friedl</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Laura Richter</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Simon Richter</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Elias Hofer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Julia Richter</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Clara Gruber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Lena Kraus</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Simon Berger</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>Workshop10</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Mia Hartmann</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sophie Fischer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Anna Meyer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lena Maier</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Emma Steiner</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mia Steiner</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Elias Lang</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Clara Wolf</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Max Huber</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Elias Graf</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Katharina Hofer</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Elias Lang</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Mia Bauer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sarah Schmidt</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tim Kraus</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3877,7 +5917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3905,7 +5945,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ben Hartmann</t>
+          <t>Felix Gruber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3922,7 +5962,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hannah Neumann</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3939,7 +5979,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Laura Müller</t>
+          <t>Tim Huber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3956,7 +5996,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Max Schwarz</t>
+          <t>Sarah Wolf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3973,7 +6013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>Anna Bauer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3990,12 +6030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lena Fischer</t>
+          <t>Lisa Koch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -4007,7 +6047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paul Hartmann</t>
+          <t>Mia Steiner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4024,7 +6064,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hannah Schulz</t>
+          <t>Fabian Graf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4041,7 +6081,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emma Klein</t>
+          <t>Sophie Richter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4058,7 +6098,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ben Schulz</t>
+          <t>Simon Auer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4070,46 +6110,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emma Schmidt</t>
+          <t>Tim Wolf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anna Schneider</t>
+          <t>Elias Lang</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>David Becker</t>
+          <t>David Schmidt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4121,29 +6161,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Nina Schmidt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mia Schulz</t>
+          <t>David Kraus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4155,12 +6195,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laura Krüger</t>
+          <t>David Weber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4172,12 +6212,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Sarah Schmidt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4189,46 +6229,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Workshop2</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greta Müller</t>
+          <t>Matteo Schmidt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Felix Koch</t>
+          <t>Katharina Wolf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tim Schwarz</t>
+          <t>Felix Huber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4240,12 +6280,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paul Neumann</t>
+          <t>Sophie Fischer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4257,12 +6297,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jonas Schneider</t>
+          <t>Felix Weber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4274,12 +6314,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Olivia Müller</t>
+          <t>Simon Hofer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4291,12 +6331,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mia Weber</t>
+          <t>Emma Bauer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4308,46 +6348,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Noah Koch</t>
+          <t>Marie Lang</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Moritz Gruber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hannah Fischer</t>
+          <t>Mia Gruber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4359,12 +6399,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tim Krüger</t>
+          <t>Anna Steiner</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4376,12 +6416,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tim Meyer</t>
+          <t>Julia Richter</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4393,12 +6433,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Workshop3</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tim Weber</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4410,29 +6450,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Emma Müller</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Felix Hoffmann</t>
+          <t>Lisa Schmidt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4444,12 +6484,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clara Koch</t>
+          <t>Emma Koch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4461,199 +6501,199 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Greta Wagner</t>
+          <t>Max Graf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mia Schneider</t>
+          <t>Jonas Auer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lena Weber</t>
+          <t>Anna Meyer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Paul Weber</t>
+          <t>Lea Leitner</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anna Lange</t>
+          <t>Marie Schwarz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Workshop4</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tim Wolf</t>
+          <t>Fabian Bauer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paul Müller</t>
+          <t>Paul Meyer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Olivia Klein</t>
+          <t>Max Huber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sara Neumann</t>
+          <t>Sarah Hofer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lena Hartmann</t>
+          <t>Emma Gruber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leon Hartmann</t>
+          <t>Jonas Bauer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Nina Wagner</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4665,12 +6705,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Workshop5</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>Lisa Müller</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4682,12 +6722,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Laura Weber</t>
+          <t>Paul Kraus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4699,63 +6739,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Tim Leitner</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laura Hoffmann</t>
+          <t>Laura Berger</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Noah Müller</t>
+          <t>Leon Auer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jonas Wagner</t>
+          <t>Noah Fischer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4767,12 +6807,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Felix Hartmann</t>
+          <t>Fabian Weber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4784,12 +6824,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nina Fischer</t>
+          <t>Clara Gruber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4801,12 +6841,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sara Schmidt</t>
+          <t>Elias Hofer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4818,46 +6858,46 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jonas Schulz</t>
+          <t>Leon Hofer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Workshop6</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Emma Zimmermann</t>
+          <t>Ben Wagner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Olivia Wolf</t>
+          <t>Fabian Wolf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4869,12 +6909,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hannah Wolf</t>
+          <t>David Maier</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4886,46 +6926,46 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sara Klein</t>
+          <t>Mia Wolf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hannah Schneider</t>
+          <t>Tim Schwarz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Hannah Weber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4937,12 +6977,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Anna Becker</t>
+          <t>Lisa Huber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4954,12 +6994,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sara Wolf</t>
+          <t>Clara Wolf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4971,12 +7011,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Workshop7</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Leon Lange</t>
+          <t>Simon Richter</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4988,114 +7028,114 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nina Becker</t>
+          <t>Tim Leitner</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Noah Krüger</t>
+          <t>Lukas Kraus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nina Krüger</t>
+          <t>Clara Koch</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Emma Lange</t>
+          <t>Sophie Bauer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Moritz Hofer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clara Lange</t>
+          <t>Simon Berger</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Clara Weber</t>
+          <t>Moritz Fischer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5107,12 +7147,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Emma Hartmann</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5124,131 +7164,131 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tim Müller</t>
+          <t>Lukas Maier</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Sophie Wagner</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lena Schmidt</t>
+          <t>Katharina Müller</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tim Hartmann</t>
+          <t>Hannah Wolf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Nina Leitner</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Laura Zimmermann</t>
+          <t>Amelie Gruber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Workshop8</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mia Hartmann</t>
+          <t>Lisa Schmidt</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Felix Meyer</t>
+          <t>Max Koch</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5260,12 +7300,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paul Krüger</t>
+          <t>Lena Maier</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5277,63 +7317,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hannah Wagner</t>
+          <t>Elias Lang</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jonas Klein</t>
+          <t>Felix Weber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ben Schwarz</t>
+          <t>Elias Graf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Greta Schneider</t>
+          <t>Ben Schmidt</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5345,12 +7385,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Max Lange</t>
+          <t>Katharina Hofer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5362,12 +7402,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mia Klein</t>
+          <t>Lisa Meyer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5379,12 +7419,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nina Neumann</t>
+          <t>Mia Bauer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5396,63 +7436,63 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mia Hoffmann</t>
+          <t>Emma Gruber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Workshop9</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nina Zimmermann</t>
+          <t>Laura Wagner</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ben Schmidt</t>
+          <t>Laura Richter</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Olivia Zimmermann</t>
+          <t>David Schmidt</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5464,12 +7504,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jonas Fischer</t>
+          <t>Lisa Maier</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5481,12 +7521,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tim Lange</t>
+          <t>Mia Müller</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5498,12 +7538,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Max Schulz</t>
+          <t>Jakob Berger</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5515,12 +7555,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Felix Neumann</t>
+          <t>Mia Schmidt</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5532,12 +7572,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nina Wolf</t>
+          <t>Hannah Weber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5549,51 +7589,1071 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Felix Wagner</t>
+          <t>Lukas Bauer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Workshop10</t>
+          <t>Workshop6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mia Schwarz</t>
+          <t>Emma Steiner</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Elias Berger</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Anna Kraus</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Marie Wolf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Amelie Müller</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fabian Berger</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Workshop6</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nina Friedl</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lisa Pichler</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hannah Graf</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nina Graf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hannah Gruber</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lisa Richter</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Paul Müller</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Lukas Wagner</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Anna Leitner</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Workshop7</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Lukas Hofer</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sarah Friedl</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Max Wolf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Simon Weber</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Amelie Koch</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Mia Wagner</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Jonas Wagner</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Laura Gruber</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Elias Friedl</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Matteo Weber</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Felix Fischer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Moritz Wagner</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Julia Pichler</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Clara Berger</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Amelie Gruber</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Lena Kraus</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Clara Friedl</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Workshop8</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jonas Huber</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Marie Lang</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Amelie Fischer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hannah Maier</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Leon Maier</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Fabian Graf</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mia Fischer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Marie Weber</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tim Kraus</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mia Friedl</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sarah Bauer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Hannah Graf</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Nina Maier</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Felix Meyer</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Lena Kraus</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Elias Graf</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Workshop9</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>David Graf</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>Workshop10</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Greta Hartmann</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Moritz Leitner</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Felix Meyer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Emma Meyer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Leon Berger</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Max Wagner</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Leon Graf</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ben Wagner</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Laura Koch</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Laura Schmidt</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Marie Friedl</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Lisa Berger</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Tim Fischer</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Workshop10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Jonas Hofer</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
